--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SForm\Nextcloud\forschung\reveald\git\docs\management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49468DA8-1FCA-43D4-B3CF-D2C24DC223EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBF6DCA-CA68-467D-A3AA-0BEE825E0FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23130" yWindow="4905" windowWidth="14400" windowHeight="8715" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -468,15 +465,33 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D20" si="0">C3-B3</f>
-        <v>0</v>
+        <v>4.166666666666663E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14583333333333326</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -579,7 +594,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>0.125</v>
+        <v>0.31249999999999989</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBF6DCA-CA68-467D-A3AA-0BEE825E0FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8306185-205D-4047-9B43-A6689E2C38F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>hrs</t>
+  </si>
+  <si>
+    <t>Meeting</t>
+  </si>
+  <si>
+    <t>Eigenarbeit</t>
   </si>
 </sst>
 </file>
@@ -71,7 +77,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,16 +94,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -432,10 +451,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46149</v>
       </c>
@@ -463,8 +482,11 @@
         <f>C2-B2</f>
         <v>0.125</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46154</v>
       </c>
@@ -478,8 +500,11 @@
         <f t="shared" ref="D3:D20" si="0">C3-B3</f>
         <v>4.166666666666663E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46162</v>
       </c>
@@ -493,74 +518,101 @@
         <f t="shared" si="0"/>
         <v>0.14583333333333326</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D5" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>46169</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0.12499999999999994</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D7" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D8" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D9" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D10" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D11" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D12" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D13" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D14" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D15" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -594,7 +646,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>0.31249999999999989</v>
+        <v>0.49999999999999983</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8306185-205D-4047-9B43-A6689E2C38F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1B9E25-6F5B-41AD-BD2A-5E96AF703CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -116,7 +116,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -554,14 +553,26 @@
         <f t="shared" si="0"/>
         <v>0.12499999999999994</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>46179</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -646,7 +657,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>0.49999999999999983</v>
+        <v>0.58333333333333304</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1B9E25-6F5B-41AD-BD2A-5E96AF703CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791044B5-1CD6-4109-BE6C-A2DE241AB236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -576,9 +576,21 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.64583333333333337</v>
+      </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -657,7 +669,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>0.58333333333333304</v>
+        <v>0.66666666666666641</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791044B5-1CD6-4109-BE6C-A2DE241AB236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F97A3D8-5E11-4BF8-93FB-477FFBF9D222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -594,9 +594,21 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -669,7 +681,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>0.66666666666666641</v>
+        <v>0.83333333333333304</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F97A3D8-5E11-4BF8-93FB-477FFBF9D222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BE2E5F-FFC2-4A85-87FE-7364F491148D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -612,9 +612,21 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -681,7 +693,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>0.83333333333333304</v>
+        <v>0.9166666666666663</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BE2E5F-FFC2-4A85-87FE-7364F491148D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE82A9-A80E-4A0D-A4DF-006316007000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -60,6 +60,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[h]:mm"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -77,7 +80,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,28 +97,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -450,10 +447,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,7 +464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46149</v>
       </c>
@@ -485,7 +482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46154</v>
       </c>
@@ -496,14 +493,14 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D20" si="0">C3-B3</f>
+        <f t="shared" ref="D3:D23" si="0">C3-B3</f>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46162</v>
       </c>
@@ -521,25 +518,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
         <v>46169</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="9">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="9">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46174</v>
       </c>
@@ -557,7 +554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46179</v>
       </c>
@@ -575,7 +572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46181</v>
       </c>
@@ -593,7 +590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46192</v>
       </c>
@@ -611,7 +608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46195</v>
       </c>
@@ -628,72 +625,158 @@
       <c r="E10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G10" s="2"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>46211</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.10416666666666663</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="D13" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <f t="shared" ref="D15" si="1">C15-B15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
       <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
+        <f t="shared" ref="D16" si="2">C16-B16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
       <c r="D17" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
+        <f t="shared" ref="D17:D20" si="3">C17-B17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
       <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
+        <f>C18-B18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
       <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
       <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C21" s="3"/>
-      <c r="D21" s="4">
-        <f>SUM(D2:D20)</f>
-        <v>0.9166666666666663</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C24" s="3"/>
+      <c r="D24" s="7">
+        <f>SUM(D2:D23)</f>
+        <v>1.4374999999999991</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE82A9-A80E-4A0D-A4DF-006316007000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B320CE5-5C43-49E7-99AD-8FE3B3784228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -110,9 +110,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -447,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -493,7 +490,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D23" si="0">C3-B3</f>
+        <f t="shared" ref="D3:D27" si="0">C3-B3</f>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="E3" t="s">
@@ -519,20 +516,20 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="8">
+      <c r="A5" s="1">
         <v>46169</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="2">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="2">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -684,99 +681,201 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46221</v>
+        <v>46218</v>
       </c>
       <c r="B14" s="2">
         <v>0.375</v>
       </c>
       <c r="C14" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>0.16666666666666663</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D15" s="2">
         <f t="shared" ref="D15" si="1">C15-B15</f>
-        <v>0</v>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D16" s="2">
         <f t="shared" ref="D16" si="2">C16-B16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D17" s="2">
         <f t="shared" ref="D17:D20" si="3">C17-B17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D18" s="2">
         <f>C18-B18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="D19" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+        <v>8.3333333333333315E-2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D20" s="2">
         <f t="shared" si="3"/>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333315E-2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D21" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D24" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D22" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D25" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D23" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D26" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C24" s="3"/>
-      <c r="D24" s="7">
-        <f>SUM(D2:D23)</f>
-        <v>1.4374999999999991</v>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C28" s="3"/>
+      <c r="D28" s="7">
+        <f>SUM(D2:D27)</f>
+        <v>1.7291666666666663</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B320CE5-5C43-49E7-99AD-8FE3B3784228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABE6D10-BA1E-4CD0-8807-6A8D4D94D3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -842,9 +842,21 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="D23" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.10416666666666663</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -875,7 +887,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="7">
         <f>SUM(D2:D27)</f>
-        <v>1.7291666666666663</v>
+        <v>1.833333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABE6D10-BA1E-4CD0-8807-6A8D4D94D3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8B62D6-E2DC-4A01-B0E2-84D7230E4974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="7">
   <si>
     <t>date</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Eigenarbeit</t>
+  </si>
+  <si>
+    <t>Urlaub</t>
   </si>
 </sst>
 </file>
@@ -80,7 +83,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -97,11 +100,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -110,6 +128,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -444,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -490,7 +509,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D27" si="0">C3-B3</f>
+        <f t="shared" ref="D3:D30" si="0">C3-B3</f>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="E3" t="s">
@@ -733,7 +752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46221</v>
       </c>
@@ -751,7 +770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46223</v>
       </c>
@@ -769,7 +788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46224</v>
       </c>
@@ -787,7 +806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46225</v>
       </c>
@@ -805,7 +824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46226</v>
       </c>
@@ -823,7 +842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46227</v>
       </c>
@@ -841,7 +860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46230</v>
       </c>
@@ -859,35 +878,123 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D24" s="2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>46244</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D24" s="4">
+        <f t="shared" si="0"/>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666741E-2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14583333333333331</v>
+      </c>
+      <c r="E28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D25" s="2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D30" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D26" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D27" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C28" s="3"/>
-      <c r="D28" s="7">
-        <f>SUM(D2:D27)</f>
-        <v>1.833333333333333</v>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C31" s="6"/>
+      <c r="D31" s="7">
+        <f>SUM(D2:D30)</f>
+        <v>2.5000000000000004</v>
+      </c>
+      <c r="F31" s="6">
+        <v>3.125</v>
+      </c>
+      <c r="G31" s="8">
+        <f>F31-D31</f>
+        <v>0.62499999999999956</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8B62D6-E2DC-4A01-B0E2-84D7230E4974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEF48AF-A18A-4EC2-9561-5A164F7ABDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="8">
   <si>
     <t>date</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Urlaub</t>
+  </si>
+  <si>
+    <t>28.-31.08.2026</t>
   </si>
 </sst>
 </file>
@@ -83,7 +86,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -115,11 +118,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -129,6 +141,7 @@
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -463,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -509,7 +522,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D30" si="0">C3-B3</f>
+        <f t="shared" ref="D3:D32" si="0">C3-B3</f>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="E3" t="s">
@@ -752,7 +765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46221</v>
       </c>
@@ -770,7 +783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46223</v>
       </c>
@@ -788,7 +801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46224</v>
       </c>
@@ -806,7 +819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46225</v>
       </c>
@@ -824,7 +837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46226</v>
       </c>
@@ -842,7 +855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46227</v>
       </c>
@@ -860,7 +873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46230</v>
       </c>
@@ -878,7 +891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>46244</v>
       </c>
@@ -896,7 +909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46253</v>
       </c>
@@ -914,7 +927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46254</v>
       </c>
@@ -932,7 +945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>46256</v>
       </c>
@@ -950,7 +963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>46258</v>
       </c>
@@ -968,33 +981,205 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.4375</v>
+      </c>
       <c r="D29" s="2">
         <f t="shared" si="0"/>
+        <v>2.0833333333333315E-2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12500000000000006</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D32" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D30" s="2">
-        <f t="shared" si="0"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C33" s="6"/>
+      <c r="D33" s="7">
+        <f>SUM(D2:D32)</f>
+        <v>2.8125000000000004</v>
+      </c>
+      <c r="F33" s="6">
+        <v>3.125</v>
+      </c>
+      <c r="G33" s="8">
+        <f>F33-D33</f>
+        <v>0.31249999999999956</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D35" s="2">
+        <f>C35-B35</f>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" ref="D36:D42" si="4">C36-B36</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="4"/>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="4"/>
+        <v>8.3333333333333315E-2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="4"/>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="4"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D41" s="2">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C31" s="6"/>
-      <c r="D31" s="7">
-        <f>SUM(D2:D30)</f>
-        <v>2.5000000000000004</v>
-      </c>
-      <c r="F31" s="6">
-        <v>3.125</v>
-      </c>
-      <c r="G31" s="8">
-        <f>F31-D31</f>
-        <v>0.62499999999999956</v>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D42" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEF48AF-A18A-4EC2-9561-5A164F7ABDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E21DE81-A762-4E49-BAED-010FE3217EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="8">
   <si>
     <t>date</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -1091,7 +1091,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" ref="D36:D42" si="4">C36-B36</f>
+        <f t="shared" ref="D36:D44" si="4">C36-B36</f>
         <v>8.333333333333337E-2</v>
       </c>
       <c r="E36" t="s">
@@ -1171,15 +1171,75 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.625</v>
+      </c>
       <c r="D41" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="D42" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="4"/>
+        <v>0.10416666666666663</v>
+      </c>
+      <c r="E43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D44" s="2">
+        <f t="shared" si="4"/>
+        <v>0.125</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E21DE81-A762-4E49-BAED-010FE3217EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EF9217-5053-4534-AA4A-FDCE2C545681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="8">
   <si>
     <t>date</t>
   </si>
@@ -86,7 +86,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -127,11 +127,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -142,6 +151,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -476,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB4B9D-C5E4-4B47-96EB-C637E3398743}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -1091,7 +1103,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" ref="D36:D44" si="4">C36-B36</f>
+        <f t="shared" ref="D36:D61" si="4">C36-B36</f>
         <v>8.333333333333337E-2</v>
       </c>
       <c r="E36" t="s">
@@ -1241,6 +1253,255 @@
       <c r="E44" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="10">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="11">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C45" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D45" s="11">
+        <f t="shared" si="4"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D46" s="2">
+        <f t="shared" si="4"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D47" s="2">
+        <f t="shared" si="4"/>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="D48" s="2">
+        <f t="shared" si="4"/>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D49" s="2">
+        <f t="shared" si="4"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D50" s="2">
+        <f t="shared" si="4"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="E50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="D51" s="2">
+        <f t="shared" si="4"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="E51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="4"/>
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="E52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D53" s="2">
+        <f t="shared" si="4"/>
+        <v>0.125</v>
+      </c>
+      <c r="E53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D54" s="2">
+        <f t="shared" si="4"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D55" s="2">
+        <f t="shared" si="4"/>
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="E55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" si="4"/>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D57" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D58" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D59" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D60" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D61" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D64" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/docs/management/studhk/studhk_timetracking.xlsx
+++ b/docs/management/studhk/studhk_timetracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHubReveald\docs\management\studhk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EF9217-5053-4534-AA4A-FDCE2C545681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CC67A3-9262-4197-AFE2-F94E64C2BE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="8">
   <si>
     <t>date</t>
   </si>
@@ -1471,33 +1471,93 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0.375</v>
+      </c>
       <c r="D57" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="D58" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="D59" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.1666666666666741E-2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="D60" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.1666666666666741E-2</v>
+      </c>
+      <c r="E60" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="D61" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
